--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N66_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N66_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>14.33741276196383</v>
+        <v>2.329829573819123</v>
       </c>
       <c r="D2" t="n">
-        <v>13.02544497407795</v>
+        <v>2.116634808287667</v>
       </c>
       <c r="E2" t="n">
-        <v>8.16758091514213</v>
+        <v>1.327231898710596</v>
       </c>
       <c r="F2" t="n">
-        <v>8.008777032288689</v>
+        <v>1.301426267746912</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.37553974129846</v>
+        <v>4.286025207960999</v>
       </c>
       <c r="D3" t="n">
-        <v>24.7018067941676</v>
+        <v>4.014043604052235</v>
       </c>
       <c r="E3" t="n">
-        <v>8.16758091514213</v>
+        <v>1.327231898710596</v>
       </c>
       <c r="F3" t="n">
-        <v>8.008777032288689</v>
+        <v>1.301426267746912</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>9.922436532474165</v>
+        <v>1.612395936527052</v>
       </c>
       <c r="D4" t="n">
-        <v>10.23659946833645</v>
+        <v>1.663447413604673</v>
       </c>
       <c r="E4" t="n">
-        <v>8.16758091514213</v>
+        <v>1.327231898710596</v>
       </c>
       <c r="F4" t="n">
-        <v>8.008777032288689</v>
+        <v>1.301426267746912</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>22.36981857768265</v>
+        <v>3.635095518873431</v>
       </c>
       <c r="D5" t="n">
-        <v>21.86407900629014</v>
+        <v>3.552912838522148</v>
       </c>
       <c r="E5" t="n">
-        <v>8.16758091514213</v>
+        <v>1.327231898710596</v>
       </c>
       <c r="F5" t="n">
-        <v>8.008777032288689</v>
+        <v>1.301426267746912</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>2.764465293524792</v>
+        <v>0.4492256101977786</v>
       </c>
       <c r="D6" t="n">
-        <v>2.264755449155985</v>
+        <v>0.3680227604878477</v>
       </c>
       <c r="E6" t="n">
-        <v>8.16758091514213</v>
+        <v>1.327231898710596</v>
       </c>
       <c r="F6" t="n">
-        <v>8.008777032288689</v>
+        <v>1.301426267746912</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>22.14495466722714</v>
+        <v>3.598555133424411</v>
       </c>
       <c r="D7" t="n">
-        <v>22.65389585506332</v>
+        <v>3.68125807644779</v>
       </c>
       <c r="E7" t="n">
-        <v>8.16758091514213</v>
+        <v>1.327231898710596</v>
       </c>
       <c r="F7" t="n">
-        <v>8.008777032288689</v>
+        <v>1.301426267746912</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
